--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-12.xlsx
@@ -757,31 +757,31 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="G2" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="H2" t="n">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="I2" t="n">
         <v>3.8</v>
       </c>
       <c r="J2" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="K2" t="n">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M2" t="n">
         <v>1.05</v>
       </c>
       <c r="N2" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
         <v>1.27</v>
@@ -790,13 +790,13 @@
         <v>1.96</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R2" t="n">
         <v>1.32</v>
       </c>
       <c r="S2" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T2" t="n">
         <v>1.01</v>
@@ -805,7 +805,7 @@
         <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W2" t="n">
         <v>1.52</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="G3" t="n">
         <v>1.83</v>
@@ -981,10 +981,10 @@
         <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="R3" t="n">
         <v>1.46</v>
@@ -993,10 +993,10 @@
         <v>2.58</v>
       </c>
       <c r="T3" t="n">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V3" t="n">
         <v>1.19</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -1533,22 +1533,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G6" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H6" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="I6" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -1921,40 +1921,40 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="G8" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="H8" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="I8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
         <v>2.16</v>
       </c>
-      <c r="J8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K8" t="n">
-        <v>7</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.14</v>
-      </c>
       <c r="Q8" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -2148,7 +2148,7 @@
         <v>2.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G10" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H10" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="I10" t="n">
         <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K10" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2342,7 +2342,7 @@
         <v>1.24</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.97</v>
+        <v>1.01</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G11" t="n">
         <v>2.28</v>
       </c>
       <c r="H11" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="I11" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
         <v>3.35</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2545,7 +2545,7 @@
         <v>4.1</v>
       </c>
       <c r="T11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="U11" t="n">
         <v>2.04</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
         <v>1.83</v>
       </c>
       <c r="G13" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H13" t="n">
         <v>4.2</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
         <v>3.3</v>
       </c>
       <c r="H14" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="I14" t="n">
         <v>2.6</v>
@@ -3115,7 +3115,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="Q14" t="n">
         <v>1.73</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -3864,19 +3864,19 @@
         <v>2.02</v>
       </c>
       <c r="G18" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="H18" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I18" t="n">
         <v>4.4</v>
       </c>
       <c r="J18" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K18" t="n">
-        <v>5.9</v>
+        <v>500</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.94</v>
+        <v>1.25</v>
       </c>
       <c r="Q18" t="n">
         <v>1.65</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q20" t="n">
         <v>1.81</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
         <v>1.91</v>
       </c>
       <c r="G21" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H21" t="n">
         <v>3.7</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4640,7 @@
         <v>2.44</v>
       </c>
       <c r="G22" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H22" t="n">
         <v>2.74</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -5034,7 +5034,7 @@
         <v>2.64</v>
       </c>
       <c r="I24" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J24" t="n">
         <v>3.7</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -5219,22 +5219,22 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="G25" t="n">
         <v>3.6</v>
       </c>
       <c r="H25" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="J25" t="n">
-        <v>1.09</v>
+        <v>1.68</v>
       </c>
       <c r="K25" t="n">
-        <v>950</v>
+        <v>5.4</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="G26" t="n">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="H26" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="I26" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="J26" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K26" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="G27" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="H27" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I27" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J27" t="n">
-        <v>3.5</v>
+        <v>2.82</v>
       </c>
       <c r="K27" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5637,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -5995,19 +5995,19 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.87</v>
+        <v>1.47</v>
       </c>
       <c r="G29" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="H29" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I29" t="n">
         <v>4</v>
       </c>
       <c r="J29" t="n">
-        <v>2.78</v>
+        <v>2.72</v>
       </c>
       <c r="K29" t="n">
         <v>950</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -6189,22 +6189,22 @@
         </is>
       </c>
       <c r="F30" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G30" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="H30" t="n">
-        <v>3.1</v>
+        <v>2.86</v>
       </c>
       <c r="I30" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="J30" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L30" t="n">
         <v>0</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -6383,19 +6383,19 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G31" t="n">
         <v>1.87</v>
       </c>
       <c r="H31" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I31" t="n">
         <v>5.6</v>
       </c>
       <c r="J31" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K31" t="n">
         <v>3.95</v>
@@ -6413,10 +6413,10 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -6774,16 +6774,16 @@
         <v>2.84</v>
       </c>
       <c r="G33" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="H33" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="I33" t="n">
-        <v>2.8</v>
+        <v>2.66</v>
       </c>
       <c r="J33" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K33" t="n">
         <v>4.1</v>
@@ -6801,10 +6801,10 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>1.9</v>
+        <v>1.04</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -6965,16 +6965,16 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="G34" t="n">
         <v>2.8</v>
       </c>
       <c r="H34" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="I34" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="J34" t="n">
         <v>3.5</v>
@@ -7001,7 +7001,7 @@
         <v>2</v>
       </c>
       <c r="R34" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S34" t="n">
         <v>3.6</v>
@@ -7010,7 +7010,7 @@
         <v>1.78</v>
       </c>
       <c r="U34" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V34" t="n">
         <v>0</v>
@@ -7019,7 +7019,7 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y34" t="n">
         <v>11.5</v>
@@ -7070,7 +7070,7 @@
         <v>27</v>
       </c>
       <c r="AO34" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AP34" t="n">
         <v>12.5</v>
@@ -7106,7 +7106,7 @@
         <v>15.5</v>
       </c>
       <c r="BA34" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB34" t="n">
         <v>36</v>
@@ -7124,11 +7124,11 @@
         <v>24</v>
       </c>
       <c r="BG34" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -7165,10 +7165,10 @@
         <v>3.3</v>
       </c>
       <c r="H35" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="I35" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="J35" t="n">
         <v>3.7</v>
@@ -7219,13 +7219,13 @@
         <v>13</v>
       </c>
       <c r="Z35" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA35" t="n">
         <v>32</v>
       </c>
       <c r="AB35" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC35" t="n">
         <v>8.199999999999999</v>
@@ -7249,7 +7249,7 @@
         <v>36</v>
       </c>
       <c r="AJ35" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AK35" t="n">
         <v>36</v>
@@ -7315,14 +7315,14 @@
         <v>55</v>
       </c>
       <c r="BF35" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BG35" t="n">
         <v>13.5</v>
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -7353,10 +7353,10 @@
         </is>
       </c>
       <c r="F36" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="G36" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H36" t="n">
         <v>2.84</v>
@@ -7368,7 +7368,7 @@
         <v>3.45</v>
       </c>
       <c r="K36" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L36" t="n">
         <v>1.42</v>
@@ -7386,7 +7386,7 @@
         <v>1.92</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="R36" t="n">
         <v>1.35</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -7547,16 +7547,16 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="G37" t="n">
         <v>7.2</v>
       </c>
       <c r="H37" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I37" t="n">
         <v>1.63</v>
-      </c>
-      <c r="I37" t="n">
-        <v>1.65</v>
       </c>
       <c r="J37" t="n">
         <v>4</v>
@@ -7577,7 +7577,7 @@
         <v>1.44</v>
       </c>
       <c r="P37" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="Q37" t="n">
         <v>2.28</v>
@@ -7604,13 +7604,13 @@
         <v>11.5</v>
       </c>
       <c r="Y37" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="Z37" t="n">
         <v>8.4</v>
       </c>
       <c r="AA37" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AB37" t="n">
         <v>17.5</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -7741,7 +7741,7 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.2</v>
+        <v>2.96</v>
       </c>
       <c r="G38" t="n">
         <v>4.3</v>
@@ -7750,10 +7750,10 @@
         <v>1.86</v>
       </c>
       <c r="I38" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="J38" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K38" t="n">
         <v>4.3</v>
@@ -7771,10 +7771,10 @@
         <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -8129,22 +8129,22 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="G40" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="H40" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I40" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="J40" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K40" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G42" t="n">
         <v>2.32</v>
@@ -8610,7 +8610,7 @@
         <v>30</v>
       </c>
       <c r="AK42" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AL42" t="n">
         <v>36</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -8714,19 +8714,19 @@
         <v>4.8</v>
       </c>
       <c r="G43" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="H43" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="I43" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="J43" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K43" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -8744,7 +8744,7 @@
         <v>1.63</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -8905,22 +8905,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G44" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H44" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I44" t="n">
         <v>3.3</v>
       </c>
       <c r="J44" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="K44" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -9099,22 +9099,22 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="G45" t="n">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="H45" t="n">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="I45" t="n">
-        <v>9.6</v>
+        <v>7.6</v>
       </c>
       <c r="J45" t="n">
         <v>3.95</v>
       </c>
       <c r="K45" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -9129,10 +9129,10 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.86</v>
+        <v>1.99</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -9293,16 +9293,16 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G46" t="n">
         <v>3.6</v>
       </c>
       <c r="H46" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I46" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="J46" t="n">
         <v>3.6</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -9681,22 +9681,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="G48" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="H48" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="I48" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K48" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -9878,16 +9878,16 @@
         <v>2.12</v>
       </c>
       <c r="G49" t="n">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="H49" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="I49" t="n">
         <v>5.2</v>
       </c>
       <c r="J49" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="K49" t="n">
         <v>3.45</v>
@@ -9908,7 +9908,7 @@
         <v>1.25</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -10263,22 +10263,22 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="G51" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H51" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="I51" t="n">
         <v>4.4</v>
       </c>
       <c r="J51" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K51" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="L51" t="n">
         <v>0</v>
@@ -10293,10 +10293,10 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -10457,19 +10457,19 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="G52" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="H52" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I52" t="n">
         <v>4.4</v>
       </c>
-      <c r="I52" t="n">
-        <v>5.5</v>
-      </c>
       <c r="J52" t="n">
-        <v>2.06</v>
+        <v>4</v>
       </c>
       <c r="K52" t="n">
         <v>950</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -10684,7 +10684,7 @@
         <v>2.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -10848,7 +10848,7 @@
         <v>2.62</v>
       </c>
       <c r="G54" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H54" t="n">
         <v>2.42</v>
@@ -10875,10 +10875,10 @@
         <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>2.04</v>
+        <v>2.2</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -11039,22 +11039,22 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="G55" t="n">
-        <v>2.76</v>
+        <v>2.94</v>
       </c>
       <c r="H55" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="I55" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="J55" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K55" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
@@ -11069,10 +11069,10 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -11233,22 +11233,22 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>1.54</v>
+        <v>2.64</v>
       </c>
       <c r="G56" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H56" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="I56" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="J56" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K56" t="n">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
@@ -11263,10 +11263,10 @@
         <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="Q56" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -11427,22 +11427,22 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="G57" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H57" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="I57" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J57" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K57" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
@@ -11457,10 +11457,10 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -11621,19 +11621,19 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G58" t="n">
-        <v>2.94</v>
+        <v>60</v>
       </c>
       <c r="H58" t="n">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="I58" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="J58" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K58" t="n">
         <v>950</v>
@@ -11651,10 +11651,10 @@
         <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.94</v>
+        <v>1.01</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -11815,22 +11815,22 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="G59" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H59" t="n">
         <v>5.3</v>
       </c>
       <c r="I59" t="n">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="J59" t="n">
         <v>4.2</v>
       </c>
       <c r="K59" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -11845,10 +11845,10 @@
         <v>0</v>
       </c>
       <c r="P59" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -12039,7 +12039,7 @@
         <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="Q60" t="n">
         <v>1.68</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -12236,7 +12236,7 @@
         <v>1.74</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="R61" t="n">
         <v>1.27</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -12397,19 +12397,19 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G62" t="n">
         <v>2</v>
       </c>
       <c r="H62" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I62" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J62" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K62" t="n">
         <v>3.6</v>
@@ -12454,31 +12454,31 @@
         <v>16</v>
       </c>
       <c r="Y62" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Z62" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA62" t="n">
         <v>1000</v>
       </c>
       <c r="AB62" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AC62" t="n">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD62" t="n">
         <v>24</v>
       </c>
       <c r="AE62" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF62" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG62" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH62" t="n">
         <v>20</v>
@@ -12487,7 +12487,7 @@
         <v>1000</v>
       </c>
       <c r="AJ62" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AK62" t="n">
         <v>24</v>
@@ -12502,19 +12502,19 @@
         <v>16.5</v>
       </c>
       <c r="AO62" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP62" t="n">
         <v>12</v>
       </c>
       <c r="AQ62" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR62" t="n">
-        <v>5.5</v>
+        <v>27</v>
       </c>
       <c r="AS62" t="n">
-        <v>6</v>
+        <v>7.2</v>
       </c>
       <c r="AT62" t="n">
         <v>8</v>
@@ -12523,10 +12523,10 @@
         <v>7</v>
       </c>
       <c r="AV62" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AW62" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="AX62" t="n">
         <v>10.5</v>
@@ -12538,7 +12538,7 @@
         <v>15.5</v>
       </c>
       <c r="BA62" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BB62" t="n">
         <v>19</v>
@@ -12550,17 +12550,17 @@
         <v>30</v>
       </c>
       <c r="BE62" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BF62" t="n">
         <v>12</v>
       </c>
       <c r="BG62" t="n">
-        <v>5.8</v>
+        <v>6.8</v>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -12591,13 +12591,13 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="G63" t="n">
         <v>1000</v>
       </c>
       <c r="H63" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="I63" t="n">
         <v>1000</v>
@@ -12630,7 +12630,7 @@
         <v>1.18</v>
       </c>
       <c r="S63" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="T63" t="n">
         <v>1.01</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -12785,22 +12785,22 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G64" t="n">
-        <v>3.3</v>
+        <v>2.86</v>
       </c>
       <c r="H64" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="I64" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="J64" t="n">
         <v>2.78</v>
       </c>
       <c r="K64" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -12815,7 +12815,7 @@
         <v>0</v>
       </c>
       <c r="P64" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q64" t="n">
         <v>1.94</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -12979,22 +12979,22 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G65" t="n">
         <v>4.6</v>
       </c>
       <c r="H65" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="I65" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="J65" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="K65" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L65" t="n">
         <v>0</v>
@@ -13009,10 +13009,10 @@
         <v>0</v>
       </c>
       <c r="P65" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -13176,13 +13176,13 @@
         <v>3.35</v>
       </c>
       <c r="G66" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H66" t="n">
         <v>2.18</v>
       </c>
       <c r="I66" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="J66" t="n">
         <v>4</v>
@@ -13197,7 +13197,7 @@
         <v>1.04</v>
       </c>
       <c r="N66" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="O66" t="n">
         <v>1.19</v>
@@ -13215,7 +13215,7 @@
         <v>2.46</v>
       </c>
       <c r="T66" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="U66" t="n">
         <v>2.76</v>
@@ -13266,7 +13266,7 @@
         <v>55</v>
       </c>
       <c r="AK66" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL66" t="n">
         <v>36</v>
@@ -13278,7 +13278,7 @@
         <v>22</v>
       </c>
       <c r="AO66" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AP66" t="n">
         <v>22</v>
@@ -13326,7 +13326,7 @@
         <v>30</v>
       </c>
       <c r="BE66" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BF66" t="n">
         <v>19.5</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G67" t="n">
         <v>1.46</v>
@@ -13472,7 +13472,7 @@
         <v>4.8</v>
       </c>
       <c r="AO67" t="n">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AP67" t="n">
         <v>27</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -14143,16 +14143,16 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="G71" t="n">
         <v>1.69</v>
       </c>
       <c r="H71" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I71" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J71" t="n">
         <v>4.5</v>
@@ -14173,10 +14173,10 @@
         <v>0</v>
       </c>
       <c r="P71" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R71" t="n">
         <v>0</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -14337,13 +14337,13 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="G72" t="n">
         <v>1.9</v>
       </c>
       <c r="H72" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I72" t="n">
         <v>5.4</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
         <v>4.1</v>
       </c>
       <c r="G73" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="H73" t="n">
         <v>1.89</v>
@@ -14543,7 +14543,7 @@
         <v>1.9</v>
       </c>
       <c r="J73" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K73" t="n">
         <v>4.3</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -14725,7 +14725,7 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>1.04</v>
+        <v>1.8</v>
       </c>
       <c r="G74" t="n">
         <v>2.36</v>
@@ -14740,7 +14740,7 @@
         <v>2.84</v>
       </c>
       <c r="K74" t="n">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="L74" t="n">
         <v>0</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -14919,22 +14919,22 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="G75" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="H75" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="I75" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="J75" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K75" t="n">
-        <v>8.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="L75" t="n">
         <v>0</v>
@@ -14952,7 +14952,7 @@
         <v>1.96</v>
       </c>
       <c r="Q75" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="R75" t="n">
         <v>0</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -15113,22 +15113,22 @@
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="G76" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="H76" t="n">
-        <v>1.89</v>
+        <v>1.04</v>
       </c>
       <c r="I76" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="J76" t="n">
-        <v>2.98</v>
+        <v>1.03</v>
       </c>
       <c r="K76" t="n">
-        <v>5.9</v>
+        <v>1000</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -15143,10 +15143,10 @@
         <v>0</v>
       </c>
       <c r="P76" t="n">
-        <v>1.64</v>
+        <v>1.08</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.86</v>
+        <v>1.01</v>
       </c>
       <c r="R76" t="n">
         <v>0</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -15307,22 +15307,22 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="G77" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="H77" t="n">
         <v>5.6</v>
       </c>
       <c r="I77" t="n">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K77" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -15337,10 +15337,10 @@
         <v>0</v>
       </c>
       <c r="P77" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="R77" t="n">
         <v>0</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -15507,10 +15507,10 @@
         <v>10.5</v>
       </c>
       <c r="H78" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="I78" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="J78" t="n">
         <v>4</v>
@@ -15537,7 +15537,7 @@
         <v>1.44</v>
       </c>
       <c r="R78" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S78" t="n">
         <v>2.12</v>
@@ -15549,7 +15549,7 @@
         <v>1.01</v>
       </c>
       <c r="V78" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="W78" t="n">
         <v>1.11</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -15698,7 +15698,7 @@
         <v>1.16</v>
       </c>
       <c r="G79" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="H79" t="n">
         <v>19.5</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -15889,7 +15889,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G80" t="n">
         <v>1.46</v>
@@ -15898,13 +15898,13 @@
         <v>8.4</v>
       </c>
       <c r="I80" t="n">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="J80" t="n">
         <v>5</v>
       </c>
       <c r="K80" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -15919,10 +15919,10 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Q80" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="R80" t="n">
         <v>0</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -16083,22 +16083,22 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G81" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="H81" t="n">
         <v>5</v>
       </c>
       <c r="I81" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="J81" t="n">
         <v>4.3</v>
       </c>
       <c r="K81" t="n">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L81" t="n">
         <v>0</v>
@@ -16113,10 +16113,10 @@
         <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="R81" t="n">
         <v>0</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -16277,22 +16277,22 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="G82" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="H82" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="I82" t="n">
         <v>4.1</v>
       </c>
       <c r="J82" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K82" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="L82" t="n">
         <v>0</v>
@@ -16307,10 +16307,10 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>1.97</v>
+        <v>1.08</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="R82" t="n">
         <v>0</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -16474,16 +16474,16 @@
         <v>2.32</v>
       </c>
       <c r="G83" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H83" t="n">
         <v>3.55</v>
       </c>
       <c r="I83" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="J83" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K83" t="n">
         <v>3.4</v>
@@ -16516,7 +16516,7 @@
         <v>1.72</v>
       </c>
       <c r="U83" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
@@ -16528,10 +16528,10 @@
         <v>14.5</v>
       </c>
       <c r="Y83" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z83" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AA83" t="n">
         <v>65</v>
@@ -16549,7 +16549,7 @@
         <v>42</v>
       </c>
       <c r="AF83" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AG83" t="n">
         <v>11.5</v>
@@ -16558,7 +16558,7 @@
         <v>16</v>
       </c>
       <c r="AI83" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ83" t="n">
         <v>32</v>
@@ -16600,7 +16600,7 @@
         <v>13.5</v>
       </c>
       <c r="AW83" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="AX83" t="n">
         <v>14</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -16665,22 +16665,22 @@
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1.51</v>
+        <v>2.42</v>
       </c>
       <c r="G84" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H84" t="n">
-        <v>2.32</v>
+        <v>2.22</v>
       </c>
       <c r="I84" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="J84" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K84" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -16695,7 +16695,7 @@
         <v>0</v>
       </c>
       <c r="P84" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q84" t="n">
         <v>1.48</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -16859,19 +16859,19 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>2.36</v>
+        <v>2.98</v>
       </c>
       <c r="G85" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H85" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I85" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="J85" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K85" t="n">
         <v>4.4</v>
@@ -16892,7 +16892,7 @@
         <v>1.61</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R85" t="n">
         <v>0</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -17062,7 +17062,7 @@
         <v>7</v>
       </c>
       <c r="I86" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="J86" t="n">
         <v>4.8</v>
@@ -17083,10 +17083,10 @@
         <v>0</v>
       </c>
       <c r="P86" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q86" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="R86" t="n">
         <v>0</v>
@@ -17095,10 +17095,10 @@
         <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>1.78</v>
+        <v>1.01</v>
       </c>
       <c r="U86" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V86" t="n">
         <v>0</v>
@@ -17161,10 +17161,10 @@
         <v>110</v>
       </c>
       <c r="AP86" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AQ86" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="AR86" t="n">
         <v>4.2</v>
@@ -17173,22 +17173,22 @@
         <v>4.3</v>
       </c>
       <c r="AT86" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU86" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV86" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="AW86" t="n">
         <v>4.2</v>
       </c>
       <c r="AX86" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY86" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ86" t="n">
         <v>18.5</v>
@@ -17197,10 +17197,10 @@
         <v>4.2</v>
       </c>
       <c r="BB86" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BC86" t="n">
-        <v>10.5</v>
+        <v>13</v>
       </c>
       <c r="BD86" t="n">
         <v>4</v>
@@ -17209,14 +17209,14 @@
         <v>4.2</v>
       </c>
       <c r="BF86" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BG86" t="n">
         <v>4.2</v>
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -17277,7 +17277,7 @@
         <v>0</v>
       </c>
       <c r="P87" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Q87" t="n">
         <v>1.98</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -17444,19 +17444,19 @@
         <v>2.74</v>
       </c>
       <c r="G88" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H88" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I88" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="J88" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K88" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -17474,7 +17474,7 @@
         <v>1.25</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="R88" t="n">
         <v>0</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -17638,10 +17638,10 @@
         <v>2.06</v>
       </c>
       <c r="G89" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H89" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="I89" t="n">
         <v>5.2</v>
@@ -17665,10 +17665,10 @@
         <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="R89" t="n">
         <v>0</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -17829,22 +17829,22 @@
         </is>
       </c>
       <c r="F90" t="n">
-        <v>1.5</v>
+        <v>2.86</v>
       </c>
       <c r="G90" t="n">
         <v>4.3</v>
       </c>
       <c r="H90" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="I90" t="n">
         <v>3</v>
       </c>
       <c r="J90" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K90" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="L90" t="n">
         <v>0</v>
@@ -17862,7 +17862,7 @@
         <v>1.56</v>
       </c>
       <c r="Q90" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="R90" t="n">
         <v>0</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -18414,7 +18414,7 @@
         <v>1.72</v>
       </c>
       <c r="G93" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="H93" t="n">
         <v>5.4</v>
@@ -18507,7 +18507,7 @@
         <v>21</v>
       </c>
       <c r="AL93" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM93" t="n">
         <v>140</v>
@@ -18528,7 +18528,7 @@
         <v>7.8</v>
       </c>
       <c r="AS93" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AT93" t="n">
         <v>7.6</v>
@@ -18540,7 +18540,7 @@
         <v>19</v>
       </c>
       <c r="AW93" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AX93" t="n">
         <v>9.199999999999999</v>
@@ -18552,7 +18552,7 @@
         <v>18</v>
       </c>
       <c r="BA93" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB93" t="n">
         <v>15.5</v>
@@ -18564,17 +18564,17 @@
         <v>30</v>
       </c>
       <c r="BE93" t="n">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF93" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BG93" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -18605,22 +18605,22 @@
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G94" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H94" t="n">
         <v>2.34</v>
       </c>
       <c r="I94" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="J94" t="n">
         <v>3.5</v>
       </c>
       <c r="K94" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L94" t="n">
         <v>0</v>
@@ -18719,13 +18719,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR94" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AS94" t="n">
         <v>24</v>
       </c>
       <c r="AT94" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU94" t="n">
         <v>7</v>
@@ -18740,13 +18740,13 @@
         <v>21</v>
       </c>
       <c r="AY94" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AZ94" t="n">
         <v>14.5</v>
       </c>
       <c r="BA94" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="BB94" t="n">
         <v>44</v>
@@ -18755,20 +18755,20 @@
         <v>29</v>
       </c>
       <c r="BD94" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE94" t="n">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="BF94" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="BG94" t="n">
         <v>16.5</v>
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -19187,22 +19187,22 @@
         </is>
       </c>
       <c r="F97" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="G97" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="H97" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="I97" t="n">
         <v>6.8</v>
       </c>
       <c r="J97" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K97" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="L97" t="n">
         <v>0</v>
@@ -19217,10 +19217,10 @@
         <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q97" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="R97" t="n">
         <v>0</v>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -19381,10 +19381,10 @@
         </is>
       </c>
       <c r="F98" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="G98" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="H98" t="n">
         <v>1.48</v>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -19587,10 +19587,10 @@
         <v>3.7</v>
       </c>
       <c r="J99" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="K99" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="L99" t="n">
         <v>0</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -19769,7 +19769,7 @@
         </is>
       </c>
       <c r="F100" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="G100" t="n">
         <v>2.86</v>
@@ -19778,7 +19778,7 @@
         <v>3.05</v>
       </c>
       <c r="I100" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J100" t="n">
         <v>2.96</v>
@@ -19799,7 +19799,7 @@
         <v>0</v>
       </c>
       <c r="P100" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="Q100" t="n">
         <v>2.74</v>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -19966,10 +19966,10 @@
         <v>2.56</v>
       </c>
       <c r="G101" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="H101" t="n">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="I101" t="n">
         <v>3.6</v>
@@ -19978,7 +19978,7 @@
         <v>2.7</v>
       </c>
       <c r="K101" t="n">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="L101" t="n">
         <v>0</v>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -20545,170 +20545,170 @@
         </is>
       </c>
       <c r="F104" t="n">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="G104" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="H104" t="n">
         <v>2.42</v>
       </c>
       <c r="I104" t="n">
-        <v>3</v>
+        <v>2.64</v>
       </c>
       <c r="J104" t="n">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="K104" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="L104" t="n">
         <v>1.01</v>
       </c>
       <c r="M104" t="n">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="N104" t="n">
-        <v>1.86</v>
+        <v>2.36</v>
       </c>
       <c r="O104" t="n">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="P104" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="Q104" t="n">
-        <v>1.02</v>
+        <v>2.48</v>
       </c>
       <c r="R104" t="n">
         <v>1.18</v>
       </c>
       <c r="S104" t="n">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="T104" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="U104" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="V104" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="W104" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X104" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Y104" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z104" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA104" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB104" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC104" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD104" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE104" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF104" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG104" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH104" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI104" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ104" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AK104" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL104" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM104" t="n">
         <v>1000</v>
       </c>
       <c r="AN104" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AO104" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AR104" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="AS104" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AT104" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AU104" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AV104" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AW104" t="n">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="AX104" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AY104" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AZ104" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BA104" t="n">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BB104" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BC104" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="BD104" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BE104" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="BF104" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG104" t="n">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -20742,16 +20742,16 @@
         <v>1.63</v>
       </c>
       <c r="G105" t="n">
-        <v>1.84</v>
+        <v>1.79</v>
       </c>
       <c r="H105" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I105" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="J105" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="K105" t="n">
         <v>4.1</v>
@@ -20769,7 +20769,7 @@
         <v>0</v>
       </c>
       <c r="P105" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q105" t="n">
         <v>1.01</v>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -21136,10 +21136,10 @@
         <v>1.61</v>
       </c>
       <c r="I107" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="J107" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K107" t="n">
         <v>4.2</v>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -21327,13 +21327,13 @@
         <v>3.3</v>
       </c>
       <c r="H108" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="I108" t="n">
         <v>2.7</v>
       </c>
       <c r="J108" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K108" t="n">
         <v>3.4</v>
@@ -21351,10 +21351,10 @@
         <v>0</v>
       </c>
       <c r="P108" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Q108" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="R108" t="n">
         <v>0</v>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -21515,19 +21515,19 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="G109" t="n">
         <v>2.16</v>
       </c>
       <c r="H109" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="I109" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="J109" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="K109" t="n">
         <v>4.9</v>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -21872,7 +21872,7 @@
       </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -21903,19 +21903,19 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="G111" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="H111" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="I111" t="n">
         <v>3.4</v>
       </c>
       <c r="J111" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K111" t="n">
         <v>4.4</v>
@@ -21933,10 +21933,10 @@
         <v>0</v>
       </c>
       <c r="P111" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="Q111" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R111" t="n">
         <v>0</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -22112,7 +22112,7 @@
         <v>2.96</v>
       </c>
       <c r="K112" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -22485,22 +22485,22 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>1.85</v>
+        <v>1.09</v>
       </c>
       <c r="G114" t="n">
-        <v>2.24</v>
+        <v>2.4</v>
       </c>
       <c r="H114" t="n">
-        <v>3.65</v>
+        <v>1.04</v>
       </c>
       <c r="I114" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J114" t="n">
-        <v>3.15</v>
+        <v>1.03</v>
       </c>
       <c r="K114" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -22515,10 +22515,10 @@
         <v>0</v>
       </c>
       <c r="P114" t="n">
-        <v>1.72</v>
+        <v>1.24</v>
       </c>
       <c r="Q114" t="n">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="R114" t="n">
         <v>0</v>
@@ -22648,7 +22648,7 @@
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -22679,7 +22679,7 @@
         </is>
       </c>
       <c r="F115" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="G115" t="n">
         <v>1.51</v>
@@ -22688,13 +22688,13 @@
         <v>8</v>
       </c>
       <c r="I115" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="J115" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K115" t="n">
-        <v>10.5</v>
+        <v>9</v>
       </c>
       <c r="L115" t="n">
         <v>0</v>
@@ -22709,10 +22709,10 @@
         <v>0</v>
       </c>
       <c r="P115" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="Q115" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R115" t="n">
         <v>0</v>
@@ -22842,7 +22842,7 @@
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -23036,7 +23036,7 @@
       </c>
       <c r="BH116" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -23230,7 +23230,7 @@
       </c>
       <c r="BH117" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>
@@ -23424,7 +23424,7 @@
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>2026-04-10 01:59:22</t>
+          <t>2026-04-10 04:31:42</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-12.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-12.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H2" t="n">
         <v>3</v>
@@ -769,13 +769,13 @@
         <v>3.25</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K2" t="n">
         <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="M2" t="n">
         <v>1.06</v>
@@ -802,13 +802,13 @@
         <v>1.72</v>
       </c>
       <c r="U2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V2" t="n">
         <v>1.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X2" t="n">
         <v>19</v>
@@ -826,7 +826,7 @@
         <v>14</v>
       </c>
       <c r="AC2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
         <v>16.5</v>
@@ -874,7 +874,7 @@
         <v>3.7</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT2" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
         <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="AX2" t="n">
         <v>14.5</v>
@@ -901,7 +901,7 @@
         <v>3.95</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BC2" t="n">
         <v>3.75</v>
@@ -910,7 +910,7 @@
         <v>3.9</v>
       </c>
       <c r="BE2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF2" t="n">
         <v>14</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -1148,16 +1148,16 @@
         <v>2.46</v>
       </c>
       <c r="G4" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H4" t="n">
         <v>2.14</v>
       </c>
       <c r="I4" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
         <v>7.8</v>
@@ -1169,22 +1169,22 @@
         <v>1.02</v>
       </c>
       <c r="N4" t="n">
-        <v>2.64</v>
+        <v>2.28</v>
       </c>
       <c r="O4" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.51</v>
+        <v>1.41</v>
       </c>
       <c r="R4" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="S4" t="n">
-        <v>2.26</v>
+        <v>2.02</v>
       </c>
       <c r="T4" t="n">
         <v>1.11</v>
@@ -1193,7 +1193,7 @@
         <v>1.11</v>
       </c>
       <c r="V4" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W4" t="n">
         <v>1.37</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1566,7 @@
         <v>1.25</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>2.12</v>
       </c>
       <c r="I7" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="J7" t="n">
         <v>3.85</v>
@@ -1775,7 +1775,7 @@
         <v>2.48</v>
       </c>
       <c r="V7" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W7" t="n">
         <v>1.4</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="G9" t="n">
         <v>2.82</v>
@@ -2130,7 +2130,7 @@
         <v>3.2</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>7.2</v>
       </c>
       <c r="L9" t="n">
         <v>1.3</v>
@@ -2145,7 +2145,7 @@
         <v>1.29</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="Q9" t="n">
         <v>1.75</v>
@@ -2166,7 +2166,7 @@
         <v>1.35</v>
       </c>
       <c r="W9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -2506,16 +2506,16 @@
         <v>3.35</v>
       </c>
       <c r="G11" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H11" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>2.2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K11" t="n">
         <v>4.2</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -2700,19 +2700,19 @@
         <v>2.66</v>
       </c>
       <c r="G12" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="H12" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I12" t="n">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="J12" t="n">
         <v>3.7</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L12" t="n">
         <v>1.01</v>
@@ -2745,10 +2745,10 @@
         <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
         <v>1.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R14" t="n">
         <v>1.29</v>
@@ -3175,7 +3175,7 @@
         <v>65</v>
       </c>
       <c r="AJ14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AK14" t="n">
         <v>26</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -3297,13 +3297,13 @@
         <v>500</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M15" t="n">
         <v>1.01</v>
       </c>
       <c r="N15" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="O15" t="n">
         <v>1.37</v>
@@ -3318,7 +3318,7 @@
         <v>1.18</v>
       </c>
       <c r="S15" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="T15" t="n">
         <v>1.11</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -3473,16 +3473,16 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="I16" t="n">
         <v>2.72</v>
-      </c>
-      <c r="G16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="H16" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I16" t="n">
-        <v>2.78</v>
       </c>
       <c r="J16" t="n">
         <v>3.6</v>
@@ -3506,13 +3506,13 @@
         <v>2.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R16" t="n">
         <v>1.43</v>
       </c>
       <c r="S16" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="T16" t="n">
         <v>1.56</v>
@@ -3521,19 +3521,19 @@
         <v>2.14</v>
       </c>
       <c r="V16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="W16" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X16" t="n">
         <v>19</v>
       </c>
       <c r="Y16" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AA16" t="n">
         <v>40</v>
@@ -3548,10 +3548,10 @@
         <v>12</v>
       </c>
       <c r="AE16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG16" t="n">
         <v>13.5</v>
@@ -3566,10 +3566,10 @@
         <v>44</v>
       </c>
       <c r="AK16" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL16" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM16" t="n">
         <v>75</v>
@@ -3590,7 +3590,7 @@
         <v>15.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.199999999999999</v>
+        <v>30</v>
       </c>
       <c r="AT16" t="n">
         <v>12</v>
@@ -3614,10 +3614,10 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC16" t="n">
         <v>24</v>
@@ -3626,17 +3626,17 @@
         <v>30</v>
       </c>
       <c r="BE16" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="BF16" t="n">
         <v>16</v>
       </c>
       <c r="BG16" t="n">
-        <v>15.5</v>
+        <v>6.4</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -3676,13 +3676,13 @@
         <v>4.2</v>
       </c>
       <c r="I17" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K17" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3697,22 +3697,22 @@
         <v>1.24</v>
       </c>
       <c r="P17" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="R17" t="n">
         <v>1.39</v>
       </c>
       <c r="S17" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
       </c>
       <c r="U17" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V17" t="n">
         <v>1.27</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -4079,13 +4079,13 @@
         <v>1.01</v>
       </c>
       <c r="N19" t="n">
-        <v>1.24</v>
+        <v>55</v>
       </c>
       <c r="O19" t="n">
         <v>1.15</v>
       </c>
       <c r="P19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q19" t="n">
         <v>1.14</v>
@@ -4094,7 +4094,7 @@
         <v>1.18</v>
       </c>
       <c r="S19" t="n">
-        <v>1.05</v>
+        <v>1.15</v>
       </c>
       <c r="T19" t="n">
         <v>1.11</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
         <v>3.15</v>
       </c>
       <c r="O20" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="P20" t="n">
         <v>1.81</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -4640,10 +4640,10 @@
         <v>1.79</v>
       </c>
       <c r="G22" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H22" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I22" t="n">
         <v>5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
         <v>1.71</v>
       </c>
       <c r="U23" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V23" t="n">
         <v>1.36</v>
@@ -4948,7 +4948,7 @@
         <v>24</v>
       </c>
       <c r="AS23" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT23" t="n">
         <v>9.6</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5067,7 @@
         <v>2.24</v>
       </c>
       <c r="T24" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="U24" t="n">
         <v>2.7</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
         <v>2.74</v>
       </c>
       <c r="I25" t="n">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="J25" t="n">
         <v>3.7</v>
@@ -5255,7 +5255,7 @@
         <v>1.58</v>
       </c>
       <c r="R25" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S25" t="n">
         <v>2.42</v>
@@ -5264,10 +5264,10 @@
         <v>1.44</v>
       </c>
       <c r="U25" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="V25" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="W25" t="n">
         <v>1.62</v>
@@ -5327,7 +5327,7 @@
         <v>20</v>
       </c>
       <c r="AP25" t="n">
-        <v>20</v>
+        <v>3.8</v>
       </c>
       <c r="AQ25" t="n">
         <v>15</v>
@@ -5375,14 +5375,14 @@
         <v>4.1</v>
       </c>
       <c r="BF25" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BG25" t="n">
         <v>12</v>
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G26" t="n">
         <v>3.15</v>
@@ -5422,10 +5422,10 @@
         <v>2.36</v>
       </c>
       <c r="I26" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="J26" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K26" t="n">
         <v>4.1</v>
@@ -5461,7 +5461,7 @@
         <v>2.24</v>
       </c>
       <c r="V26" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W26" t="n">
         <v>1.46</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
         <v>2.8</v>
       </c>
       <c r="H27" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="I27" t="n">
         <v>2.78</v>
@@ -5631,28 +5631,28 @@
         <v>1.05</v>
       </c>
       <c r="N27" t="n">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="O27" t="n">
         <v>1.23</v>
       </c>
       <c r="P27" t="n">
-        <v>1.38</v>
+        <v>1.85</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.73</v>
+        <v>1.23</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S27" t="n">
         <v>2.52</v>
       </c>
       <c r="T27" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V27" t="n">
         <v>1.57</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5804,7 @@
         <v>3.05</v>
       </c>
       <c r="G28" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="H28" t="n">
         <v>2.04</v>
@@ -5813,7 +5813,7 @@
         <v>2.26</v>
       </c>
       <c r="J28" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K28" t="n">
         <v>980</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6213,7 @@
         <v>1.04</v>
       </c>
       <c r="N30" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="O30" t="n">
         <v>1.19</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G32" t="n">
         <v>2.28</v>
@@ -6592,7 +6592,7 @@
         <v>4.1</v>
       </c>
       <c r="K32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="L32" t="n">
         <v>1.01</v>
@@ -6607,22 +6607,22 @@
         <v>1.13</v>
       </c>
       <c r="P32" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="R32" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="T32" t="n">
         <v>1.42</v>
       </c>
       <c r="U32" t="n">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="V32" t="n">
         <v>1.44</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -6771,7 +6771,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G33" t="n">
         <v>2.3</v>
@@ -6795,16 +6795,16 @@
         <v>1.04</v>
       </c>
       <c r="N33" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="O33" t="n">
         <v>1.21</v>
       </c>
       <c r="P33" t="n">
-        <v>2.28</v>
+        <v>1.54</v>
       </c>
       <c r="Q33" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="R33" t="n">
         <v>1.47</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -6965,22 +6965,22 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="G34" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="H34" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="I34" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J34" t="n">
         <v>3.7</v>
       </c>
       <c r="K34" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="L34" t="n">
         <v>1.01</v>
@@ -6989,19 +6989,19 @@
         <v>1.07</v>
       </c>
       <c r="N34" t="n">
-        <v>1.73</v>
+        <v>1.78</v>
       </c>
       <c r="O34" t="n">
         <v>1.33</v>
       </c>
       <c r="P34" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R34" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S34" t="n">
         <v>3.2</v>
@@ -7013,10 +7013,10 @@
         <v>1.01</v>
       </c>
       <c r="V34" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W34" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="X34" t="n">
         <v>1000</v>
@@ -7076,7 +7076,7 @@
         <v>10</v>
       </c>
       <c r="AQ34" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR34" t="n">
         <v>25</v>
@@ -7085,25 +7085,25 @@
         <v>40</v>
       </c>
       <c r="AT34" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU34" t="n">
         <v>6.8</v>
       </c>
       <c r="AV34" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AW34" t="n">
         <v>40</v>
       </c>
       <c r="AX34" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AY34" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ34" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA34" t="n">
         <v>40</v>
@@ -7112,10 +7112,10 @@
         <v>14.5</v>
       </c>
       <c r="BC34" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BD34" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BE34" t="n">
         <v>40</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G35" t="n">
         <v>2.58</v>
@@ -7168,7 +7168,7 @@
         <v>3.15</v>
       </c>
       <c r="I35" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J35" t="n">
         <v>3</v>
@@ -7207,7 +7207,7 @@
         <v>1.89</v>
       </c>
       <c r="V35" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W35" t="n">
         <v>1.62</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
         <v>2.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="R36" t="n">
         <v>1.34</v>
@@ -7395,10 +7395,10 @@
         <v>2.62</v>
       </c>
       <c r="T36" t="n">
-        <v>1.11</v>
+        <v>1.54</v>
       </c>
       <c r="U36" t="n">
-        <v>1.11</v>
+        <v>2.08</v>
       </c>
       <c r="V36" t="n">
         <v>1.59</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -7589,16 +7589,16 @@
         <v>3.75</v>
       </c>
       <c r="T37" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U37" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V37" t="n">
         <v>1.54</v>
       </c>
       <c r="W37" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X37" t="n">
         <v>13.5</v>
@@ -7607,7 +7607,7 @@
         <v>11</v>
       </c>
       <c r="Z37" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA37" t="n">
         <v>44</v>
@@ -7622,7 +7622,7 @@
         <v>12.5</v>
       </c>
       <c r="AE37" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AF37" t="n">
         <v>17.5</v>
@@ -7640,7 +7640,7 @@
         <v>42</v>
       </c>
       <c r="AK37" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AL37" t="n">
         <v>44</v>
@@ -7649,7 +7649,7 @@
         <v>100</v>
       </c>
       <c r="AN37" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO37" t="n">
         <v>29</v>
@@ -7664,7 +7664,7 @@
         <v>16.5</v>
       </c>
       <c r="AS37" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AT37" t="n">
         <v>10.5</v>
@@ -7688,7 +7688,7 @@
         <v>16.5</v>
       </c>
       <c r="BA37" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BB37" t="n">
         <v>38</v>
@@ -7700,7 +7700,7 @@
         <v>40</v>
       </c>
       <c r="BE37" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BF37" t="n">
         <v>26</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -7741,10 +7741,10 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G38" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="H38" t="n">
         <v>2.34</v>
@@ -7765,7 +7765,7 @@
         <v>1.06</v>
       </c>
       <c r="N38" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O38" t="n">
         <v>1.26</v>
@@ -7789,7 +7789,7 @@
         <v>2.4</v>
       </c>
       <c r="V38" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="W38" t="n">
         <v>1.43</v>
@@ -7846,7 +7846,7 @@
         <v>27</v>
       </c>
       <c r="AO38" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AP38" t="n">
         <v>16</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -7938,7 +7938,7 @@
         <v>2.82</v>
       </c>
       <c r="G39" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H39" t="n">
         <v>2.76</v>
@@ -7959,7 +7959,7 @@
         <v>1.07</v>
       </c>
       <c r="N39" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="O39" t="n">
         <v>1.34</v>
@@ -7983,7 +7983,7 @@
         <v>2.18</v>
       </c>
       <c r="V39" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W39" t="n">
         <v>1.53</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -8326,10 +8326,10 @@
         <v>6.8</v>
       </c>
       <c r="G41" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="H41" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="I41" t="n">
         <v>1.64</v>
@@ -8392,7 +8392,7 @@
         <v>18</v>
       </c>
       <c r="AC41" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD41" t="n">
         <v>10.5</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
         <v>2.36</v>
       </c>
       <c r="I42" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="J42" t="n">
         <v>3.25</v>
@@ -8547,7 +8547,7 @@
         <v>1.36</v>
       </c>
       <c r="P42" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Q42" t="n">
         <v>2.06</v>
@@ -8577,64 +8577,64 @@
         <v>11.5</v>
       </c>
       <c r="Z42" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AA42" t="n">
         <v>40</v>
       </c>
       <c r="AB42" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AD42" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AE42" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AF42" t="n">
         <v>27</v>
       </c>
       <c r="AG42" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="AH42" t="n">
         <v>20</v>
       </c>
       <c r="AI42" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AJ42" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AK42" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AL42" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM42" t="n">
         <v>120</v>
       </c>
       <c r="AN42" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AO42" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AP42" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="AQ42" t="n">
-        <v>3.65</v>
+        <v>4.9</v>
       </c>
       <c r="AR42" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.7</v>
+        <v>7.2</v>
       </c>
       <c r="AT42" t="n">
         <v>10.5</v>
@@ -8646,41 +8646,41 @@
         <v>10</v>
       </c>
       <c r="AW42" t="n">
-        <v>4.6</v>
+        <v>6.6</v>
       </c>
       <c r="AX42" t="n">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AY42" t="n">
-        <v>4</v>
+        <v>5.5</v>
       </c>
       <c r="AZ42" t="n">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BA42" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB42" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="BC42" t="n">
-        <v>4.8</v>
+        <v>7.2</v>
       </c>
       <c r="BD42" t="n">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BE42" t="n">
-        <v>5.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF42" t="n">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG42" t="n">
-        <v>17</v>
+        <v>6.4</v>
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -8735,7 +8735,7 @@
         <v>1.01</v>
       </c>
       <c r="N43" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="O43" t="n">
         <v>1.25</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -8944,7 +8944,7 @@
         <v>1.25</v>
       </c>
       <c r="S44" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="T44" t="n">
         <v>1.11</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -9293,22 +9293,22 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="G46" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="H46" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I46" t="n">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J46" t="n">
-        <v>1.09</v>
+        <v>3.35</v>
       </c>
       <c r="K46" t="n">
-        <v>1000</v>
+        <v>4.8</v>
       </c>
       <c r="L46" t="n">
         <v>1.34</v>
@@ -9341,10 +9341,10 @@
         <v>1.11</v>
       </c>
       <c r="V46" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W46" t="n">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="X46" t="n">
         <v>1000</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
         <v>2.66</v>
       </c>
       <c r="I47" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="J47" t="n">
         <v>2.68</v>
@@ -9514,7 +9514,7 @@
         <v>2.5</v>
       </c>
       <c r="O47" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P47" t="n">
         <v>1.7</v>
@@ -9526,7 +9526,7 @@
         <v>1.25</v>
       </c>
       <c r="S47" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="T47" t="n">
         <v>1.11</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -9875,10 +9875,10 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="G49" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="H49" t="n">
         <v>6.8</v>
@@ -9890,7 +9890,7 @@
         <v>4.2</v>
       </c>
       <c r="K49" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L49" t="n">
         <v>1.37</v>
@@ -9926,7 +9926,7 @@
         <v>1.14</v>
       </c>
       <c r="W49" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="X49" t="n">
         <v>18.5</v>
@@ -9935,7 +9935,7 @@
         <v>26</v>
       </c>
       <c r="Z49" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AA49" t="n">
         <v>270</v>
@@ -10004,7 +10004,7 @@
         <v>19.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="AX49" t="n">
         <v>8</v>
@@ -10034,11 +10034,11 @@
         <v>6.8</v>
       </c>
       <c r="BG49" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
         <v>17.5</v>
       </c>
       <c r="AP50" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="AQ50" t="n">
         <v>9.4</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
         <v>1.01</v>
       </c>
       <c r="N52" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="O52" t="n">
         <v>1.13</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -10663,7 +10663,7 @@
         <v>4.5</v>
       </c>
       <c r="J53" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K53" t="n">
         <v>3.45</v>
@@ -10702,7 +10702,7 @@
         <v>1.3</v>
       </c>
       <c r="W53" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="X53" t="n">
         <v>1000</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -10869,7 +10869,7 @@
         <v>1.01</v>
       </c>
       <c r="N54" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="O54" t="n">
         <v>1.31</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -11051,10 +11051,10 @@
         <v>4.5</v>
       </c>
       <c r="J55" t="n">
-        <v>1.03</v>
+        <v>1.09</v>
       </c>
       <c r="K55" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="L55" t="n">
         <v>1.01</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -11257,7 +11257,7 @@
         <v>1.02</v>
       </c>
       <c r="N56" t="n">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="O56" t="n">
         <v>1.11</v>
@@ -11272,7 +11272,7 @@
         <v>1.89</v>
       </c>
       <c r="S56" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="T56" t="n">
         <v>1.4</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -11624,13 +11624,13 @@
         <v>2.64</v>
       </c>
       <c r="G58" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H58" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="I58" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J58" t="n">
         <v>3.65</v>
@@ -11654,7 +11654,7 @@
         <v>2.2</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R58" t="n">
         <v>1.48</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -12591,22 +12591,22 @@
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="G63" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="H63" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="I63" t="n">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="J63" t="n">
         <v>4.3</v>
       </c>
       <c r="K63" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="L63" t="n">
         <v>1.01</v>
@@ -12618,7 +12618,7 @@
         <v>2.34</v>
       </c>
       <c r="O63" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="P63" t="n">
         <v>2.34</v>
@@ -12639,10 +12639,10 @@
         <v>1.01</v>
       </c>
       <c r="V63" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W63" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="X63" t="n">
         <v>1000</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -12815,10 +12815,10 @@
         <v>1.25</v>
       </c>
       <c r="P64" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="R64" t="n">
         <v>1.35</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -13370,7 +13370,7 @@
         <v>2.3</v>
       </c>
       <c r="G67" t="n">
-        <v>110</v>
+        <v>2.82</v>
       </c>
       <c r="H67" t="n">
         <v>3.15</v>
@@ -13379,7 +13379,7 @@
         <v>4.2</v>
       </c>
       <c r="J67" t="n">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="K67" t="n">
         <v>3.85</v>
@@ -13418,7 +13418,7 @@
         <v>1.31</v>
       </c>
       <c r="W67" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="X67" t="n">
         <v>1000</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -13585,7 +13585,7 @@
         <v>1.01</v>
       </c>
       <c r="N68" t="n">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="O68" t="n">
         <v>1.45</v>
@@ -13597,10 +13597,10 @@
         <v>2.14</v>
       </c>
       <c r="R68" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S68" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="T68" t="n">
         <v>1.96</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
         <v>1.04</v>
       </c>
       <c r="N69" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="O69" t="n">
         <v>1.2</v>
@@ -13788,19 +13788,19 @@
         <v>2.62</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R69" t="n">
         <v>1.64</v>
       </c>
       <c r="S69" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="T69" t="n">
         <v>1.55</v>
       </c>
       <c r="U69" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="V69" t="n">
         <v>1.82</v>
@@ -13830,7 +13830,7 @@
         <v>10.5</v>
       </c>
       <c r="AE69" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AF69" t="n">
         <v>27</v>
@@ -13839,7 +13839,7 @@
         <v>14</v>
       </c>
       <c r="AH69" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AI69" t="n">
         <v>26</v>
@@ -13899,7 +13899,7 @@
         <v>24</v>
       </c>
       <c r="BB69" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BC69" t="n">
         <v>29</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -14066,7 +14066,7 @@
         <v>34</v>
       </c>
       <c r="AS70" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="AT70" t="n">
         <v>12</v>
@@ -14075,10 +14075,10 @@
         <v>11.5</v>
       </c>
       <c r="AV70" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AW70" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AX70" t="n">
         <v>10</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
         <v>1.48</v>
       </c>
       <c r="O71" t="n">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="P71" t="n">
         <v>1.48</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14361,7 @@
         <v>1.01</v>
       </c>
       <c r="N72" t="n">
-        <v>1.79</v>
+        <v>2.96</v>
       </c>
       <c r="O72" t="n">
         <v>1.29</v>
@@ -14373,16 +14373,16 @@
         <v>1.8</v>
       </c>
       <c r="R72" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S72" t="n">
-        <v>1.8</v>
+        <v>2.58</v>
       </c>
       <c r="T72" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U72" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V72" t="n">
         <v>1.01</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -14555,7 +14555,7 @@
         <v>1.01</v>
       </c>
       <c r="N73" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
       <c r="O73" t="n">
         <v>1.3</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -14925,7 +14925,7 @@
         <v>1.9</v>
       </c>
       <c r="H75" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I75" t="n">
         <v>5.6</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -15125,7 +15125,7 @@
         <v>1.86</v>
       </c>
       <c r="J76" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K76" t="n">
         <v>4.3</v>
@@ -15215,7 +15215,7 @@
         <v>80</v>
       </c>
       <c r="AN76" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AO76" t="n">
         <v>10.5</v>
@@ -15269,14 +15269,14 @@
         <v>11</v>
       </c>
       <c r="BF76" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BG76" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -15307,13 +15307,13 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="G77" t="n">
         <v>1.89</v>
       </c>
       <c r="H77" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="I77" t="n">
         <v>7.6</v>
@@ -15337,7 +15337,7 @@
         <v>1.25</v>
       </c>
       <c r="P77" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="Q77" t="n">
         <v>1.61</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -15528,7 +15528,7 @@
         <v>1.47</v>
       </c>
       <c r="O78" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P78" t="n">
         <v>1.47</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -16483,7 +16483,7 @@
         <v>1.62</v>
       </c>
       <c r="J83" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K83" t="n">
         <v>5.4</v>
@@ -16555,7 +16555,7 @@
         <v>30</v>
       </c>
       <c r="AH83" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI83" t="n">
         <v>36</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -16671,7 +16671,7 @@
         <v>1.18</v>
       </c>
       <c r="H84" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I84" t="n">
         <v>30</v>
@@ -16710,7 +16710,7 @@
         <v>2.12</v>
       </c>
       <c r="U84" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="V84" t="n">
         <v>1.03</v>
@@ -16767,7 +16767,7 @@
         <v>310</v>
       </c>
       <c r="AN84" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="AO84" t="n">
         <v>590</v>
@@ -16776,13 +16776,13 @@
         <v>6.4</v>
       </c>
       <c r="AQ84" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AR84" t="n">
         <v>6.8</v>
       </c>
-      <c r="AR84" t="n">
+      <c r="AS84" t="n">
         <v>7</v>
-      </c>
-      <c r="AS84" t="n">
-        <v>7.2</v>
       </c>
       <c r="AT84" t="n">
         <v>11</v>
@@ -16794,7 +16794,7 @@
         <v>6.6</v>
       </c>
       <c r="AW84" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX84" t="n">
         <v>7.8</v>
@@ -16803,10 +16803,10 @@
         <v>10.5</v>
       </c>
       <c r="AZ84" t="n">
-        <v>40</v>
+        <v>6.2</v>
       </c>
       <c r="BA84" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BB84" t="n">
         <v>7.8</v>
@@ -16818,7 +16818,7 @@
         <v>6.2</v>
       </c>
       <c r="BE84" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BF84" t="n">
         <v>2.44</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -16859,10 +16859,10 @@
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="G85" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="H85" t="n">
         <v>8.6</v>
@@ -16889,10 +16889,10 @@
         <v>1.23</v>
       </c>
       <c r="P85" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q85" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="R85" t="n">
         <v>1.5</v>
@@ -16901,16 +16901,16 @@
         <v>2.74</v>
       </c>
       <c r="T85" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="U85" t="n">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="V85" t="n">
         <v>1.1</v>
       </c>
       <c r="W85" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="X85" t="n">
         <v>22</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -17441,16 +17441,16 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="G88" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="H88" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I88" t="n">
         <v>3.6</v>
-      </c>
-      <c r="I88" t="n">
-        <v>3.65</v>
       </c>
       <c r="J88" t="n">
         <v>3.35</v>
@@ -17477,7 +17477,7 @@
         <v>1.92</v>
       </c>
       <c r="R88" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S88" t="n">
         <v>3.25</v>
@@ -17489,10 +17489,10 @@
         <v>2.32</v>
       </c>
       <c r="V88" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W88" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="X88" t="n">
         <v>14.5</v>
@@ -17543,7 +17543,7 @@
         <v>80</v>
       </c>
       <c r="AN88" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AO88" t="n">
         <v>36</v>
@@ -17591,7 +17591,7 @@
         <v>21</v>
       </c>
       <c r="BD88" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE88" t="n">
         <v>34</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -17659,19 +17659,19 @@
         <v>1.01</v>
       </c>
       <c r="N89" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O89" t="n">
         <v>1.15</v>
       </c>
       <c r="P89" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="R89" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S89" t="n">
         <v>2.12</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -18259,10 +18259,10 @@
         <v>4</v>
       </c>
       <c r="T92" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="U92" t="n">
-        <v>1.87</v>
+        <v>1.96</v>
       </c>
       <c r="V92" t="n">
         <v>1.44</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -18411,7 +18411,7 @@
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1.51</v>
+        <v>2.34</v>
       </c>
       <c r="G93" t="n">
         <v>4.3</v>
@@ -18420,13 +18420,13 @@
         <v>2.26</v>
       </c>
       <c r="I93" t="n">
-        <v>2.98</v>
+        <v>2.82</v>
       </c>
       <c r="J93" t="n">
-        <v>2.32</v>
+        <v>2.42</v>
       </c>
       <c r="K93" t="n">
-        <v>110</v>
+        <v>7.6</v>
       </c>
       <c r="L93" t="n">
         <v>1.01</v>
@@ -18459,7 +18459,7 @@
         <v>1.01</v>
       </c>
       <c r="V93" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="W93" t="n">
         <v>1.3</v>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -18620,7 +18620,7 @@
         <v>2.9</v>
       </c>
       <c r="K94" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L94" t="n">
         <v>1.55</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -19020,7 +19020,7 @@
         <v>2.56</v>
       </c>
       <c r="O96" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P96" t="n">
         <v>1.59</v>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -19199,7 +19199,7 @@
         <v>4.5</v>
       </c>
       <c r="J97" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="K97" t="n">
         <v>6.8</v>
@@ -19211,7 +19211,7 @@
         <v>1.01</v>
       </c>
       <c r="N97" t="n">
-        <v>1.82</v>
+        <v>3.05</v>
       </c>
       <c r="O97" t="n">
         <v>1.26</v>
@@ -19223,16 +19223,16 @@
         <v>1.72</v>
       </c>
       <c r="R97" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="S97" t="n">
-        <v>1.72</v>
+        <v>2.36</v>
       </c>
       <c r="T97" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U97" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V97" t="n">
         <v>1.28</v>
@@ -19350,7 +19350,7 @@
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -19384,16 +19384,16 @@
         <v>1.76</v>
       </c>
       <c r="G98" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="H98" t="n">
         <v>5.4</v>
       </c>
       <c r="I98" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J98" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="K98" t="n">
         <v>4.1</v>
@@ -19444,7 +19444,7 @@
         <v>48</v>
       </c>
       <c r="AA98" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AB98" t="n">
         <v>8.4</v>
@@ -19471,10 +19471,10 @@
         <v>85</v>
       </c>
       <c r="AJ98" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK98" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AL98" t="n">
         <v>40</v>
@@ -19495,7 +19495,7 @@
         <v>16.5</v>
       </c>
       <c r="AR98" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AS98" t="n">
         <v>15.5</v>
@@ -19510,7 +19510,7 @@
         <v>19</v>
       </c>
       <c r="AW98" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="AX98" t="n">
         <v>9.199999999999999</v>
@@ -19540,11 +19540,11 @@
         <v>10</v>
       </c>
       <c r="BG98" t="n">
-        <v>14.5</v>
+        <v>65</v>
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -19683,7 +19683,7 @@
         <v>21</v>
       </c>
       <c r="AP99" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ99" t="n">
         <v>10</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -19796,7 +19796,7 @@
         <v>1.76</v>
       </c>
       <c r="O100" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P100" t="n">
         <v>1.76</v>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -20375,13 +20375,13 @@
         <v>1.01</v>
       </c>
       <c r="N103" t="n">
-        <v>1.25</v>
+        <v>1.1</v>
       </c>
       <c r="O103" t="n">
         <v>1.09</v>
       </c>
       <c r="P103" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Q103" t="n">
         <v>1.09</v>
@@ -20390,7 +20390,7 @@
         <v>1.24</v>
       </c>
       <c r="S103" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="T103" t="n">
         <v>1.11</v>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -20551,13 +20551,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="H104" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="I104" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="J104" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="K104" t="n">
         <v>5.2</v>
@@ -20566,13 +20566,13 @@
         <v>1.01</v>
       </c>
       <c r="M104" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N104" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O104" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P104" t="n">
         <v>2.28</v>
@@ -20581,134 +20581,134 @@
         <v>1.7</v>
       </c>
       <c r="R104" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S104" t="n">
         <v>2.78</v>
       </c>
       <c r="T104" t="n">
-        <v>1.11</v>
+        <v>1.87</v>
       </c>
       <c r="U104" t="n">
-        <v>1.11</v>
+        <v>2.04</v>
       </c>
       <c r="V104" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="W104" t="n">
         <v>1.13</v>
       </c>
       <c r="X104" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y104" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z104" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA104" t="n">
+        <v>14</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>27</v>
+      </c>
+      <c r="AC104" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD104" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AE104" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AF104" t="n">
+        <v>70</v>
+      </c>
+      <c r="AG104" t="n">
+        <v>29</v>
+      </c>
+      <c r="AH104" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI104" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ104" t="n">
+        <v>260</v>
+      </c>
+      <c r="AK104" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL104" t="n">
+        <v>110</v>
+      </c>
+      <c r="AM104" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN104" t="n">
+        <v>140</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP104" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ104" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR104" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS104" t="n">
         <v>12</v>
       </c>
-      <c r="Z104" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AA104" t="n">
-        <v>18</v>
-      </c>
-      <c r="AB104" t="n">
-        <v>30</v>
-      </c>
-      <c r="AC104" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD104" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE104" t="n">
-        <v>20</v>
-      </c>
-      <c r="AF104" t="n">
-        <v>75</v>
-      </c>
-      <c r="AG104" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH104" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI104" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ104" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK104" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL104" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM104" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN104" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO104" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP104" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AQ104" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AR104" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AS104" t="n">
-        <v>2</v>
-      </c>
       <c r="AT104" t="n">
-        <v>19.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU104" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV104" t="n">
-        <v>1.92</v>
+        <v>8.6</v>
       </c>
       <c r="AW104" t="n">
-        <v>2.02</v>
+        <v>13.5</v>
       </c>
       <c r="AX104" t="n">
-        <v>44</v>
+        <v>11</v>
       </c>
       <c r="AY104" t="n">
         <v>20</v>
       </c>
       <c r="AZ104" t="n">
-        <v>2.08</v>
+        <v>17.5</v>
       </c>
       <c r="BA104" t="n">
-        <v>2.14</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB104" t="n">
-        <v>2.24</v>
+        <v>12.5</v>
       </c>
       <c r="BC104" t="n">
-        <v>2.24</v>
+        <v>11.5</v>
       </c>
       <c r="BD104" t="n">
-        <v>2.24</v>
+        <v>11.5</v>
       </c>
       <c r="BE104" t="n">
-        <v>2.24</v>
+        <v>12</v>
       </c>
       <c r="BF104" t="n">
-        <v>2.24</v>
+        <v>12</v>
       </c>
       <c r="BG104" t="n">
-        <v>2.24</v>
+        <v>5.4</v>
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -20757,16 +20757,16 @@
         <v>2.9</v>
       </c>
       <c r="L105" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="M105" t="n">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="N105" t="n">
-        <v>1.39</v>
+        <v>2.18</v>
       </c>
       <c r="O105" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="P105" t="n">
         <v>1.39</v>
@@ -20775,16 +20775,16 @@
         <v>3.25</v>
       </c>
       <c r="R105" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="S105" t="n">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="T105" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="U105" t="n">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="V105" t="n">
         <v>1.35</v>
@@ -20793,116 +20793,116 @@
         <v>1.61</v>
       </c>
       <c r="X105" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="Y105" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="Z105" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AA105" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB105" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AC105" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="AD105" t="n">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="AE105" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AF105" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AG105" t="n">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="AH105" t="n">
         <v>38</v>
       </c>
       <c r="AI105" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AJ105" t="n">
+        <v>44</v>
+      </c>
+      <c r="AK105" t="n">
         <v>48</v>
       </c>
-      <c r="AK105" t="n">
-        <v>55</v>
-      </c>
       <c r="AL105" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM105" t="n">
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="AN105" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AO105" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AP105" t="n">
-        <v>3.05</v>
+        <v>5.8</v>
       </c>
       <c r="AQ105" t="n">
         <v>7.6</v>
       </c>
       <c r="AR105" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="AS105" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AT105" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AU105" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV105" t="n">
         <v>16</v>
       </c>
       <c r="AW105" t="n">
-        <v>50</v>
+        <v>14.5</v>
       </c>
       <c r="AX105" t="n">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AY105" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ105" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA105" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="BB105" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BC105" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="BD105" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="BE105" t="n">
-        <v>5.2</v>
+        <v>17</v>
       </c>
       <c r="BF105" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="BG105" t="n">
-        <v>5.1</v>
+        <v>16</v>
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -20936,7 +20936,7 @@
         <v>2.62</v>
       </c>
       <c r="G106" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="H106" t="n">
         <v>3.05</v>
@@ -20945,7 +20945,7 @@
         <v>3.4</v>
       </c>
       <c r="J106" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="K106" t="n">
         <v>3.25</v>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -21127,40 +21127,40 @@
         </is>
       </c>
       <c r="F107" t="n">
-        <v>1.04</v>
+        <v>2.06</v>
       </c>
       <c r="G107" t="n">
         <v>3.55</v>
       </c>
       <c r="H107" t="n">
-        <v>1.39</v>
+        <v>2.74</v>
       </c>
       <c r="I107" t="n">
-        <v>3.7</v>
+        <v>870</v>
       </c>
       <c r="J107" t="n">
-        <v>1.39</v>
+        <v>1.97</v>
       </c>
       <c r="K107" t="n">
-        <v>4.2</v>
+        <v>500</v>
       </c>
       <c r="L107" t="n">
-        <v>1.54</v>
+        <v>1.01</v>
       </c>
       <c r="M107" t="n">
         <v>1.01</v>
       </c>
       <c r="N107" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="O107" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P107" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Q107" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="R107" t="n">
         <v>1.18</v>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -21345,7 +21345,7 @@
         <v>1.01</v>
       </c>
       <c r="N108" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="O108" t="n">
         <v>1.27</v>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -21515,7 +21515,7 @@
         </is>
       </c>
       <c r="F109" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G109" t="n">
         <v>2.82</v>
@@ -21533,19 +21533,19 @@
         <v>110</v>
       </c>
       <c r="L109" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M109" t="n">
         <v>1.01</v>
       </c>
       <c r="N109" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="O109" t="n">
         <v>1.41</v>
       </c>
       <c r="P109" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="Q109" t="n">
         <v>1.41</v>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -21709,55 +21709,55 @@
         </is>
       </c>
       <c r="F110" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="G110" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="H110" t="n">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="I110" t="n">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="J110" t="n">
-        <v>3.1</v>
+        <v>2.94</v>
       </c>
       <c r="K110" t="n">
         <v>3.3</v>
       </c>
       <c r="L110" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="M110" t="n">
         <v>1.11</v>
       </c>
       <c r="N110" t="n">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="O110" t="n">
-        <v>1.61</v>
+        <v>1.56</v>
       </c>
       <c r="P110" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="Q110" t="n">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="R110" t="n">
         <v>1.19</v>
       </c>
       <c r="S110" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T110" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="U110" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="V110" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="W110" t="n">
         <v>1.36</v>
@@ -21766,7 +21766,7 @@
         <v>970</v>
       </c>
       <c r="Y110" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="Z110" t="n">
         <v>970</v>
@@ -21775,7 +21775,7 @@
         <v>38</v>
       </c>
       <c r="AB110" t="n">
-        <v>9.800000000000001</v>
+        <v>970</v>
       </c>
       <c r="AC110" t="n">
         <v>970</v>
@@ -21793,86 +21793,86 @@
         <v>970</v>
       </c>
       <c r="AH110" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI110" t="n">
+        <v>75</v>
+      </c>
+      <c r="AJ110" t="n">
+        <v>100</v>
+      </c>
+      <c r="AK110" t="n">
         <v>70</v>
       </c>
-      <c r="AJ110" t="n">
-        <v>110</v>
-      </c>
-      <c r="AK110" t="n">
-        <v>80</v>
-      </c>
       <c r="AL110" t="n">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="AM110" t="n">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="AN110" t="n">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AO110" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="AP110" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AQ110" t="n">
         <v>4.5</v>
       </c>
-      <c r="AQ110" t="n">
-        <v>6.2</v>
-      </c>
       <c r="AR110" t="n">
-        <v>5.6</v>
+        <v>11.5</v>
       </c>
       <c r="AS110" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT110" t="n">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="AU110" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="AV110" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AW110" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="AX110" t="n">
-        <v>6.6</v>
+        <v>20</v>
       </c>
       <c r="AY110" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AZ110" t="n">
-        <v>6.8</v>
+        <v>2.28</v>
       </c>
       <c r="BA110" t="n">
-        <v>8</v>
+        <v>2.42</v>
       </c>
       <c r="BB110" t="n">
-        <v>8.4</v>
+        <v>2.44</v>
       </c>
       <c r="BC110" t="n">
-        <v>8</v>
+        <v>2.42</v>
       </c>
       <c r="BD110" t="n">
-        <v>8.4</v>
+        <v>2.44</v>
       </c>
       <c r="BE110" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BF110" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BG110" t="n">
         <v>8.6</v>
       </c>
-      <c r="BF110" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BG110" t="n">
-        <v>7.4</v>
-      </c>
       <c r="BH110" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -21903,7 +21903,7 @@
         </is>
       </c>
       <c r="F111" t="n">
-        <v>1.69</v>
+        <v>1.74</v>
       </c>
       <c r="G111" t="n">
         <v>2.3</v>
@@ -21921,22 +21921,22 @@
         <v>5.8</v>
       </c>
       <c r="L111" t="n">
-        <v>1.58</v>
+        <v>1.01</v>
       </c>
       <c r="M111" t="n">
         <v>1.01</v>
       </c>
       <c r="N111" t="n">
-        <v>1.25</v>
+        <v>2.26</v>
       </c>
       <c r="O111" t="n">
         <v>1.01</v>
       </c>
       <c r="P111" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="Q111" t="n">
-        <v>1.54</v>
+        <v>2.08</v>
       </c>
       <c r="R111" t="n">
         <v>1.17</v>
@@ -21945,10 +21945,10 @@
         <v>4.3</v>
       </c>
       <c r="T111" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U111" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V111" t="n">
         <v>1.19</v>
@@ -22066,7 +22066,7 @@
       </c>
       <c r="BH111" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -22097,7 +22097,7 @@
         </is>
       </c>
       <c r="F112" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="G112" t="n">
         <v>1.89</v>
@@ -22115,13 +22115,13 @@
         <v>950</v>
       </c>
       <c r="L112" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M112" t="n">
         <v>1.01</v>
       </c>
       <c r="N112" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="O112" t="n">
         <v>1.38</v>
@@ -22260,7 +22260,7 @@
       </c>
       <c r="BH112" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -22294,7 +22294,7 @@
         <v>1.04</v>
       </c>
       <c r="G113" t="n">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="H113" t="n">
         <v>1.04</v>
@@ -22309,13 +22309,13 @@
         <v>1000</v>
       </c>
       <c r="L113" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="M113" t="n">
         <v>1.01</v>
       </c>
       <c r="N113" t="n">
-        <v>1.62</v>
+        <v>1.1</v>
       </c>
       <c r="O113" t="n">
         <v>1.05</v>
@@ -22333,13 +22333,13 @@
         <v>1.05</v>
       </c>
       <c r="T113" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U113" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V113" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W113" t="n">
         <v>1.01</v>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="BH113" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -22485,31 +22485,31 @@
         </is>
       </c>
       <c r="F114" t="n">
-        <v>2.2</v>
+        <v>3.9</v>
       </c>
       <c r="G114" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="H114" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="I114" t="n">
         <v>1.87</v>
       </c>
       <c r="J114" t="n">
-        <v>2.16</v>
+        <v>2.62</v>
       </c>
       <c r="K114" t="n">
         <v>1000</v>
       </c>
       <c r="L114" t="n">
-        <v>1.43</v>
+        <v>1.01</v>
       </c>
       <c r="M114" t="n">
         <v>1.01</v>
       </c>
       <c r="N114" t="n">
-        <v>1.61</v>
+        <v>2.54</v>
       </c>
       <c r="O114" t="n">
         <v>1.38</v>
@@ -22527,16 +22527,16 @@
         <v>3.3</v>
       </c>
       <c r="T114" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U114" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V114" t="n">
         <v>2.14</v>
       </c>
       <c r="W114" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X114" t="n">
         <v>1000</v>
@@ -22648,7 +22648,7 @@
       </c>
       <c r="BH114" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -22691,7 +22691,7 @@
         <v>3.55</v>
       </c>
       <c r="J115" t="n">
-        <v>2.16</v>
+        <v>2.52</v>
       </c>
       <c r="K115" t="n">
         <v>5.3</v>
@@ -22703,7 +22703,7 @@
         <v>1.01</v>
       </c>
       <c r="N115" t="n">
-        <v>1.51</v>
+        <v>2.34</v>
       </c>
       <c r="O115" t="n">
         <v>1.33</v>
@@ -22718,13 +22718,13 @@
         <v>1.18</v>
       </c>
       <c r="S115" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="T115" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U115" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V115" t="n">
         <v>1.39</v>
@@ -22842,7 +22842,7 @@
       </c>
       <c r="BH115" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -22873,7 +22873,7 @@
         </is>
       </c>
       <c r="F116" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="G116" t="n">
         <v>2.94</v>
@@ -22888,10 +22888,10 @@
         <v>3.2</v>
       </c>
       <c r="K116" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L116" t="n">
-        <v>1.48</v>
+        <v>1.01</v>
       </c>
       <c r="M116" t="n">
         <v>1.01</v>
@@ -22990,10 +22990,10 @@
         <v>12.5</v>
       </c>
       <c r="AS116" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AT116" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU116" t="n">
         <v>5.9</v>
@@ -23011,7 +23011,7 @@
         <v>9.6</v>
       </c>
       <c r="AZ116" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA116" t="n">
         <v>40</v>
@@ -23036,7 +23036,7 @@
       </c>
       <c r="BH116" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -23073,164 +23073,164 @@
         <v>3.3</v>
       </c>
       <c r="H117" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I117" t="n">
         <v>2.78</v>
       </c>
       <c r="J117" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K117" t="n">
         <v>3.4</v>
       </c>
       <c r="L117" t="n">
-        <v>1.5</v>
+        <v>1.01</v>
       </c>
       <c r="M117" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N117" t="n">
         <v>2.96</v>
       </c>
       <c r="O117" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="P117" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="Q117" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R117" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="S117" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="T117" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U117" t="n">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V117" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W117" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X117" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD117" t="n">
         <v>12.5</v>
       </c>
-      <c r="Y117" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z117" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA117" t="n">
+      <c r="AE117" t="n">
+        <v>34</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>60</v>
+      </c>
+      <c r="AK117" t="n">
         <v>44</v>
       </c>
-      <c r="AB117" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC117" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD117" t="n">
+      <c r="AL117" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>8</v>
+      </c>
+      <c r="AR117" t="n">
         <v>14</v>
       </c>
-      <c r="AE117" t="n">
-        <v>38</v>
-      </c>
-      <c r="AF117" t="n">
-        <v>24</v>
-      </c>
-      <c r="AG117" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH117" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI117" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ117" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK117" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL117" t="n">
-        <v>75</v>
-      </c>
-      <c r="AM117" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN117" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO117" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP117" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AQ117" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR117" t="n">
-        <v>12</v>
-      </c>
       <c r="AS117" t="n">
-        <v>4.4</v>
+        <v>34</v>
       </c>
       <c r="AT117" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="AU117" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV117" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AW117" t="n">
-        <v>4.4</v>
+        <v>28</v>
       </c>
       <c r="AX117" t="n">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="AY117" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ117" t="n">
         <v>17</v>
       </c>
       <c r="BA117" t="n">
-        <v>4.6</v>
+        <v>38</v>
       </c>
       <c r="BB117" t="n">
-        <v>4.6</v>
+        <v>9.4</v>
       </c>
       <c r="BC117" t="n">
-        <v>4.5</v>
+        <v>36</v>
       </c>
       <c r="BD117" t="n">
-        <v>4.6</v>
+        <v>9.6</v>
       </c>
       <c r="BE117" t="n">
-        <v>4.8</v>
+        <v>10.5</v>
       </c>
       <c r="BF117" t="n">
-        <v>4.5</v>
+        <v>32</v>
       </c>
       <c r="BG117" t="n">
-        <v>4.4</v>
+        <v>22</v>
       </c>
       <c r="BH117" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="F118" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="G118" t="n">
         <v>2</v>
@@ -23270,19 +23270,19 @@
         <v>4.5</v>
       </c>
       <c r="I118" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="J118" t="n">
         <v>3.4</v>
       </c>
       <c r="K118" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L118" t="n">
-        <v>1.44</v>
+        <v>1.01</v>
       </c>
       <c r="M118" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N118" t="n">
         <v>1.78</v>
@@ -23309,13 +23309,13 @@
         <v>1.01</v>
       </c>
       <c r="V118" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W118" t="n">
         <v>2</v>
       </c>
       <c r="X118" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Y118" t="n">
         <v>1000</v>
@@ -23372,59 +23372,59 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.06</v>
+        <v>10</v>
       </c>
       <c r="AR118" t="n">
-        <v>1.06</v>
+        <v>24</v>
       </c>
       <c r="AS118" t="n">
-        <v>1.06</v>
+        <v>70</v>
       </c>
       <c r="AT118" t="n">
-        <v>1.06</v>
+        <v>6.6</v>
       </c>
       <c r="AU118" t="n">
-        <v>1.06</v>
+        <v>6.6</v>
       </c>
       <c r="AV118" t="n">
-        <v>1.06</v>
+        <v>14</v>
       </c>
       <c r="AW118" t="n">
-        <v>1.06</v>
+        <v>42</v>
       </c>
       <c r="AX118" t="n">
-        <v>1.06</v>
+        <v>9</v>
       </c>
       <c r="AY118" t="n">
-        <v>1.06</v>
+        <v>9</v>
       </c>
       <c r="AZ118" t="n">
-        <v>1.06</v>
+        <v>17.5</v>
       </c>
       <c r="BA118" t="n">
-        <v>1.06</v>
+        <v>44</v>
       </c>
       <c r="BB118" t="n">
-        <v>1.06</v>
+        <v>17</v>
       </c>
       <c r="BC118" t="n">
-        <v>1.06</v>
+        <v>17</v>
       </c>
       <c r="BD118" t="n">
-        <v>1.06</v>
+        <v>29</v>
       </c>
       <c r="BE118" t="n">
-        <v>1.06</v>
+        <v>80</v>
       </c>
       <c r="BF118" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="BG118" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="BH118" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -23458,7 +23458,7 @@
         <v>2.66</v>
       </c>
       <c r="G119" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="H119" t="n">
         <v>2.98</v>
@@ -23482,7 +23482,7 @@
         <v>2.36</v>
       </c>
       <c r="O119" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P119" t="n">
         <v>1.56</v>
@@ -23506,7 +23506,7 @@
         <v>1.41</v>
       </c>
       <c r="W119" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X119" t="n">
         <v>11.5</v>
@@ -23618,7 +23618,7 @@
       </c>
       <c r="BH119" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -23649,170 +23649,170 @@
         </is>
       </c>
       <c r="F120" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="G120" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="H120" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="J120" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="K120" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M120" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="P120" t="n">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="Q120" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S120" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T120" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U120" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="V120" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W120" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="X120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP120" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ120" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR120" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AS120" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AT120" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU120" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AV120" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AW120" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AX120" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY120" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ120" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BA120" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="BB120" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BC120" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD120" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BE120" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="BF120" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG120" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH120" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -23843,7 +23843,7 @@
         </is>
       </c>
       <c r="F121" t="n">
-        <v>1.82</v>
+        <v>1.32</v>
       </c>
       <c r="G121" t="n">
         <v>2.18</v>
@@ -23855,22 +23855,22 @@
         <v>6</v>
       </c>
       <c r="J121" t="n">
-        <v>2.68</v>
+        <v>2.96</v>
       </c>
       <c r="K121" t="n">
-        <v>5.7</v>
+        <v>500</v>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="M121" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N121" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="O121" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P121" t="n">
         <v>1.74</v>
@@ -23879,134 +23879,134 @@
         <v>1.86</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S121" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T121" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U121" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V121" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W121" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="X121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO121" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP121" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ121" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AR121" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AS121" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT121" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AU121" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AV121" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AW121" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX121" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY121" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ121" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BA121" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BB121" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BC121" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BD121" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="BE121" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF121" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG121" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH121" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -24055,152 +24055,152 @@
         <v>1000</v>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O122" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P122" t="n">
         <v>1.24</v>
       </c>
       <c r="Q122" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S122" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO122" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG122" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH122" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -24231,13 +24231,13 @@
         </is>
       </c>
       <c r="F123" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="G123" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="H123" t="n">
-        <v>8.199999999999999</v>
+        <v>3.05</v>
       </c>
       <c r="I123" t="n">
         <v>1000</v>
@@ -24246,19 +24246,19 @@
         <v>4.3</v>
       </c>
       <c r="K123" t="n">
-        <v>9.800000000000001</v>
+        <v>950</v>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M123" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="O123" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P123" t="n">
         <v>1.79</v>
@@ -24267,134 +24267,134 @@
         <v>1.8</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S123" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="T123" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U123" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V123" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W123" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="X123" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y123" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z123" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA123" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB123" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC123" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD123" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE123" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF123" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG123" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH123" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI123" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ123" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK123" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL123" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM123" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN123" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO123" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP123" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AR123" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AS123" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT123" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AU123" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV123" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AW123" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX123" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AY123" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ123" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="BA123" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB123" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BC123" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BD123" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE123" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF123" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG123" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH123" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -24425,170 +24425,170 @@
         </is>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="G124" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="H124" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="J124" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="K124" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="O124" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P124" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="Q124" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S124" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T124" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U124" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V124" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W124" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X124" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA124" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB124" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC124" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD124" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE124" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF124" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG124" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH124" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI124" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ124" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK124" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL124" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM124" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN124" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO124" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP124" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ124" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR124" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AS124" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT124" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU124" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV124" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AW124" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AX124" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AY124" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ124" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA124" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BB124" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC124" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BD124" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BE124" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="BF124" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG124" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH124" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -24637,152 +24637,152 @@
         <v>1000</v>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M125" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N125" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="O125" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P125" t="n">
-        <v>1.12</v>
+        <v>1.32</v>
       </c>
       <c r="Q125" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="R125" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S125" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T125" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U125" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V125" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W125" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X125" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y125" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z125" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA125" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB125" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC125" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD125" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE125" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF125" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG125" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH125" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI125" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ125" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK125" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL125" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM125" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN125" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO125" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP125" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AQ125" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AR125" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AS125" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT125" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU125" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV125" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AW125" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AX125" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY125" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AZ125" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA125" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BB125" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BC125" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BD125" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BE125" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BF125" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG125" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH125" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
@@ -24831,152 +24831,152 @@
         <v>0</v>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M126" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O126" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P126" t="n">
         <v>1.24</v>
       </c>
       <c r="Q126" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S126" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T126" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="U126" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V126" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W126" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X126" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y126" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z126" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA126" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB126" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC126" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD126" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF126" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG126" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH126" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI126" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ126" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK126" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL126" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM126" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN126" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO126" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP126" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AQ126" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR126" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AS126" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT126" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AU126" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV126" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AW126" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AX126" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AY126" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ126" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA126" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BB126" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BC126" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD126" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BE126" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BF126" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG126" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH126" t="inlineStr">
         <is>
-          <t>2026-04-10 19:45:27</t>
+          <t>2026-04-10 22:17:48</t>
         </is>
       </c>
     </row>
